--- a/output/pdf_financials_xlsx/RCH.xlsx
+++ b/output/pdf_financials_xlsx/RCH.xlsx
@@ -2351,7 +2351,7 @@
         <v>0.005</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.761</v>
+        <v>6.761</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>7.898</v>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>118.518</v>
+        <v>124.518</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>202.639</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>10.50840544758122</v>
+        <v>11.04039580082281</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>14.06808866327506</v>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.299</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.348</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -7034,51 +7034,49 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.351</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.218</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.643</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.104</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.997</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>0.005</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>7.898</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>10.636</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>10.857</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>10.819</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>10.894</v>
       </c>
     </row>
     <row r="101">
@@ -9053,20 +9051,14 @@
       <c r="P130" s="3" t="n">
         <v>58.707</v>
       </c>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q130" s="3" t="n">
+        <v>157.857</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="S130" s="3" t="n">
+        <v>-12.284</v>
       </c>
     </row>
     <row r="131">
@@ -9193,10 +9185,10 @@
         <v>-134.147</v>
       </c>
       <c r="R132" s="3" t="n">
-        <v>-168.709</v>
+        <v>-35.994</v>
       </c>
       <c r="S132" s="3" t="n">
-        <v>-166.638</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="133">
@@ -9249,25 +9241,19 @@
         <v>0.928</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>0.073</v>
+        <v>58.707</v>
       </c>
       <c r="P133" s="3" t="n">
         <v>-111.988</v>
       </c>
-      <c r="Q133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q133" s="3" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>-12.284</v>
+      </c>
+      <c r="S133" s="3" t="n">
+        <v>22.636</v>
       </c>
     </row>
     <row r="134">
@@ -9394,10 +9380,10 @@
         <v>0</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>0</v>
+        <v>132.715</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>0</v>
+        <v>201.558</v>
       </c>
     </row>
   </sheetData>
@@ -23666,7 +23652,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -25478,7 +25464,11 @@
           <t>Net cash and cash equivalents (net of bank overdraft), beginning of year</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -25582,7 +25572,11 @@
           <t>Net cash and cash equivalents (net of bank overdraft), end of year</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -25874,7 +25868,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -26966,7 +26960,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -27808,7 +27802,11 @@
           <t>Cash and cash equivalents and (bank overdraft), end of year</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -28414,7 +28412,11 @@
           <t>Cash and cash equivalents and bank overdraft, end of year</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28836,7 +28838,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -30732,7 +30734,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -32076,7 +32078,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -34242,7 +34244,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E243" s="5" t="n">
@@ -36528,7 +36530,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -38062,7 +38064,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -39604,7 +39606,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -40758,7 +40760,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -41066,7 +41068,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E311" s="5" t="n">
@@ -41694,7 +41696,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -42654,7 +42656,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -44030,7 +44032,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -45840,7 +45842,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
